--- a/data/trans_orig/P24C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>55850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78719</t>
+          <t>80785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>27262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>46033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88150</t>
+          <t>88480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119545</t>
+          <t>119119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58089</t>
+          <t>58579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44274</t>
+          <t>43440</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66739</t>
+          <t>65532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96024</t>
+          <t>94714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>50583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44768</t>
+          <t>46390</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73594</t>
+          <t>73972</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58267</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81799</t>
+          <t>81688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44749</t>
+          <t>46023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>68842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110187</t>
+          <t>111052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143601</t>
+          <t>143807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>33588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56710</t>
+          <t>56192</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39592</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62105</t>
+          <t>61977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78120</t>
+          <t>78060</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109644</t>
+          <t>109805</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36521</t>
+          <t>36764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36494</t>
+          <t>37096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>60999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74625</t>
+          <t>76718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106390</t>
+          <t>106256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94882</t>
+          <t>96106</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128273</t>
+          <t>128530</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93425</t>
+          <t>91325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126388</t>
+          <t>123276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>105020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140137</t>
+          <t>138461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44549</t>
+          <t>44182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72420</t>
+          <t>70603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55975</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84822</t>
+          <t>82101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221518</t>
+          <t>220349</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>270068</t>
+          <t>268987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70407</t>
+          <t>70504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99961</t>
+          <t>99229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>301780</t>
+          <t>299929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>358583</t>
+          <t>356874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185671</t>
+          <t>187887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232932</t>
+          <t>233722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87963</t>
+          <t>88338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119331</t>
+          <t>118875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>288849</t>
+          <t>288264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342906</t>
+          <t>342959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92002</t>
+          <t>90793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129752</t>
+          <t>130133</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67069</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140465</t>
+          <t>141227</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184590</t>
+          <t>186630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61147</t>
+          <t>61628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88674</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57946</t>
+          <t>57158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83759</t>
+          <t>82916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127603</t>
+          <t>127305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164042</t>
+          <t>164330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>58996</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85824</t>
+          <t>85329</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62595</t>
+          <t>62760</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>87241</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126587</t>
+          <t>125635</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164023</t>
+          <t>163869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28987</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52339</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47575</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60320</t>
+          <t>59867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91631</t>
+          <t>91067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43600</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>62184</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68209</t>
+          <t>67821</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93395</t>
+          <t>93032</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>115557</t>
+          <t>118098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147618</t>
+          <t>149281</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57660</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81043</t>
+          <t>81662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83545</t>
+          <t>81424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114373</t>
+          <t>112956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>38127</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560904</t>
+          <t>562152</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>636199</t>
+          <t>635705</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>319071</t>
+          <t>320844</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>377211</t>
+          <t>376200</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>900715</t>
+          <t>895596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>990391</t>
+          <t>996321</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>472383</t>
+          <t>472598</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>548090</t>
+          <t>545307</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>318601</t>
+          <t>320550</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>375299</t>
+          <t>373916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>809582</t>
+          <t>807331</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>904234</t>
+          <t>899720</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>243634</t>
+          <t>243721</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>305787</t>
+          <t>302317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>143524</t>
+          <t>145493</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>190656</t>
+          <t>190912</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>401956</t>
+          <t>400417</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>477218</t>
+          <t>479085</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24506</t>
+          <t>25411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48039</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43320</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>70639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>49896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75280</t>
+          <t>75541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32270</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87463</t>
+          <t>88803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120755</t>
+          <t>120854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37030</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61461</t>
+          <t>62350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46211</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>72403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103555</t>
+          <t>103180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>19246</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>38670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32514</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>58140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45494</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72144</t>
+          <t>71115</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>41045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64565</t>
+          <t>64341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>91720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>128039</t>
+          <t>127104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49941</t>
+          <t>50972</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76558</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44288</t>
+          <t>44797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69058</t>
+          <t>69181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103317</t>
+          <t>103692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>139600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43821</t>
+          <t>43876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56917</t>
+          <t>57473</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113217</t>
+          <t>112842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148075</t>
+          <t>146760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>55263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157612</t>
+          <t>157931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197796</t>
+          <t>195878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92724</t>
+          <t>91808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125571</t>
+          <t>125600</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116262</t>
+          <t>115503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153654</t>
+          <t>154802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63295</t>
+          <t>62289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96442</t>
+          <t>96904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89934</t>
+          <t>89413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>130439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207543</t>
+          <t>208755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255045</t>
+          <t>255370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117262</t>
+          <t>116357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151289</t>
+          <t>150587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335296</t>
+          <t>337440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395419</t>
+          <t>392982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>165115</t>
+          <t>163701</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>210155</t>
+          <t>209204</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>104266</t>
+          <t>102859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138649</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>279119</t>
+          <t>278595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338852</t>
+          <t>335529</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56307</t>
+          <t>55503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>53567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84585</t>
+          <t>85082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91742</t>
+          <t>92429</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122051</t>
+          <t>122953</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100071</t>
+          <t>98136</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130953</t>
+          <t>129842</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>203340</t>
+          <t>202781</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>245610</t>
+          <t>247631</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53400</t>
+          <t>53888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81533</t>
+          <t>82009</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59827</t>
+          <t>61563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88626</t>
+          <t>89619</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119379</t>
+          <t>121444</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160169</t>
+          <t>160749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>23014</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45247</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>41348</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>67048</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>27160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>42353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72363</t>
+          <t>71769</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98100</t>
+          <t>97512</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103586</t>
+          <t>104637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>134191</t>
+          <t>133676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58774</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41221</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66613</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>210608</t>
+          <t>206727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>263105</t>
+          <t>262808</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116707</t>
+          <t>115940</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161916</t>
+          <t>161048</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>337174</t>
+          <t>337754</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>412358</t>
+          <t>408143</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>587924</t>
+          <t>585808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>665904</t>
+          <t>662129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>444725</t>
+          <t>443278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>508645</t>
+          <t>509512</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1050347</t>
+          <t>1048573</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1148943</t>
+          <t>1149553</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>443901</t>
+          <t>447349</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>520257</t>
+          <t>517910</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>330572</t>
+          <t>328896</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>392003</t>
+          <t>391023</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>796352</t>
+          <t>794747</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>893368</t>
+          <t>887581</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016 (tasa de respuesta: 97,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>30884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51188</t>
+          <t>52191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>29827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44235</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>64789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92071</t>
+          <t>91875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>35938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55962</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27503</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53555</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78577</t>
+          <t>77925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>24945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>37995</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>59460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32163</t>
+          <t>32230</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>52057</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>75383</t>
+          <t>74497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>104472</t>
+          <t>104296</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47240</t>
+          <t>48158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46840</t>
+          <t>46967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60546</t>
+          <t>61081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88657</t>
+          <t>89060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>36564</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43927</t>
+          <t>44796</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87911</t>
+          <t>87676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119180</t>
+          <t>117580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111080</t>
+          <t>111180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144555</t>
+          <t>144691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70762</t>
+          <t>73854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103514</t>
+          <t>103443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91289</t>
+          <t>91940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123530</t>
+          <t>124539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85132</t>
+          <t>85636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55179</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>94352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130256</t>
+          <t>133027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179983</t>
+          <t>181447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221256</t>
+          <t>225026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120128</t>
+          <t>119386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156215</t>
+          <t>153827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312243</t>
+          <t>311750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365803</t>
+          <t>366282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134988</t>
+          <t>133289</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172646</t>
+          <t>174036</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>110302</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144655</t>
+          <t>145240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>253892</t>
+          <t>253058</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>305816</t>
+          <t>306550</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37678</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65207</t>
+          <t>67402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>111009</t>
+          <t>111102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>141474</t>
+          <t>142829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>82159</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>109727</t>
+          <t>111010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>202167</t>
+          <t>201918</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>242623</t>
+          <t>246043</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69370</t>
+          <t>68234</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100052</t>
+          <t>98904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79831</t>
+          <t>78196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107479</t>
+          <t>106266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153959</t>
+          <t>153833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197379</t>
+          <t>195574</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35343</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30861</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53437</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40328</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72474</t>
+          <t>73340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100448</t>
+          <t>98891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118382</t>
+          <t>120043</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152398</t>
+          <t>150913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>62,88%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>44736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69749</t>
+          <t>69514</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48880</t>
+          <t>50004</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77390</t>
+          <t>77818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>150341</t>
+          <t>150516</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>201104</t>
+          <t>202921</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>104927</t>
+          <t>101245</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143298</t>
+          <t>141787</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>267564</t>
+          <t>268459</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>333874</t>
+          <t>332686</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>535842</t>
+          <t>535366</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>602543</t>
+          <t>605558</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>398215</t>
+          <t>396063</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>456641</t>
+          <t>454198</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>946321</t>
+          <t>946333</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1039523</t>
+          <t>1038188</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>383344</t>
+          <t>380485</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>447749</t>
+          <t>445748</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>324188</t>
+          <t>322678</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>380648</t>
+          <t>380689</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>723820</t>
+          <t>721579</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>813388</t>
+          <t>806485</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55850</t>
+          <t>54870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80785</t>
+          <t>79334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46033</t>
+          <t>46216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88480</t>
+          <t>90102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119119</t>
+          <t>120125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>58526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>42643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65532</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94714</t>
+          <t>94885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>50087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>29278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46390</t>
+          <t>46247</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73972</t>
+          <t>75211</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58148</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81688</t>
+          <t>82490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46023</t>
+          <t>44370</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68842</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111052</t>
+          <t>108887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143807</t>
+          <t>142955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33588</t>
+          <t>31722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56192</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>40085</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61977</t>
+          <t>61945</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78060</t>
+          <t>77173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109805</t>
+          <t>109685</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36764</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37096</t>
+          <t>35772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60999</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76718</t>
+          <t>75148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106256</t>
+          <t>106042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>27714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96106</t>
+          <t>94210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128530</t>
+          <t>128909</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91325</t>
+          <t>92347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123276</t>
+          <t>124299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105020</t>
+          <t>105054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138461</t>
+          <t>138041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44182</t>
+          <t>45402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70603</t>
+          <t>71894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>53952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82101</t>
+          <t>82850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>220349</t>
+          <t>220074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268987</t>
+          <t>267346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70504</t>
+          <t>69007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99229</t>
+          <t>100112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299929</t>
+          <t>301500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356874</t>
+          <t>355131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187887</t>
+          <t>185982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233722</t>
+          <t>233938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88338</t>
+          <t>88572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118875</t>
+          <t>119908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>288264</t>
+          <t>290925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342959</t>
+          <t>346875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90793</t>
+          <t>91357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130133</t>
+          <t>130525</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>40398</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66085</t>
+          <t>65486</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>141227</t>
+          <t>140901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>186630</t>
+          <t>187240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61628</t>
+          <t>62128</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>89336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57158</t>
+          <t>57374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82916</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127305</t>
+          <t>127755</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164330</t>
+          <t>166285</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>57096</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>85430</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62760</t>
+          <t>62183</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87241</t>
+          <t>88534</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>125635</t>
+          <t>125426</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>163869</t>
+          <t>163642</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28357</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52943</t>
+          <t>51599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>49484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>60226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91067</t>
+          <t>93685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43259</t>
+          <t>41623</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>60571</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67821</t>
+          <t>66763</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93032</t>
+          <t>91977</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>118098</t>
+          <t>117852</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149281</t>
+          <t>149485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55520</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81662</t>
+          <t>81795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81424</t>
+          <t>82334</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112956</t>
+          <t>114891</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>30749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38127</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>562152</t>
+          <t>564226</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>635705</t>
+          <t>636441</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>320844</t>
+          <t>321374</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>376200</t>
+          <t>377281</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>895596</t>
+          <t>903204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>996321</t>
+          <t>992742</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>472598</t>
+          <t>475264</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>545307</t>
+          <t>547175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>320550</t>
+          <t>318026</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>373916</t>
+          <t>374724</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>807331</t>
+          <t>810703</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>899720</t>
+          <t>897565</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>243721</t>
+          <t>241311</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>302317</t>
+          <t>301392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>145493</t>
+          <t>145763</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>190912</t>
+          <t>193052</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>400417</t>
+          <t>401481</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>479085</t>
+          <t>478216</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25411</t>
+          <t>24858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>48774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42923</t>
+          <t>42622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70639</t>
+          <t>70589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49896</t>
+          <t>50355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75541</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>53285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88803</t>
+          <t>87475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120854</t>
+          <t>120145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62350</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47277</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72403</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103180</t>
+          <t>102613</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>38548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>32131</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>57663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>45799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91720</t>
+          <t>94820</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>127104</t>
+          <t>128794</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50972</t>
+          <t>51132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78282</t>
+          <t>77042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44797</t>
+          <t>44402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103692</t>
+          <t>102746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139600</t>
+          <t>138728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43876</t>
+          <t>43573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>31641</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57473</t>
+          <t>55580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112842</t>
+          <t>110831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146760</t>
+          <t>147093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37306</t>
+          <t>37636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55263</t>
+          <t>55982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157931</t>
+          <t>157562</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195878</t>
+          <t>196388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91808</t>
+          <t>91915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125600</t>
+          <t>127201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115503</t>
+          <t>116423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154802</t>
+          <t>154628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62289</t>
+          <t>62914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>97255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89413</t>
+          <t>87314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130439</t>
+          <t>129759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>208755</t>
+          <t>208103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255370</t>
+          <t>252955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116357</t>
+          <t>116573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150587</t>
+          <t>151797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337440</t>
+          <t>336748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392982</t>
+          <t>394057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163701</t>
+          <t>164357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>209204</t>
+          <t>209076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102859</t>
+          <t>101999</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>135657</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>278595</t>
+          <t>278808</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>335529</t>
+          <t>337261</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31869</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55503</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>17188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>54335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85082</t>
+          <t>84055</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>92604</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122953</t>
+          <t>123210</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98136</t>
+          <t>100560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129842</t>
+          <t>130933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>202781</t>
+          <t>201923</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>247631</t>
+          <t>244840</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82009</t>
+          <t>81169</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61563</t>
+          <t>60130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89619</t>
+          <t>88820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121444</t>
+          <t>121197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160749</t>
+          <t>162553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>26512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23014</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>45177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66987</t>
+          <t>66882</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>41586</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71769</t>
+          <t>71905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97512</t>
+          <t>98311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>104637</t>
+          <t>103862</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133676</t>
+          <t>133419</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35043</t>
+          <t>35335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58385</t>
+          <t>58498</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67394</t>
+          <t>67752</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>206727</t>
+          <t>207564</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>262808</t>
+          <t>266745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115940</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161048</t>
+          <t>159700</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>337754</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>408143</t>
+          <t>412962</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>585808</t>
+          <t>586326</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>662129</t>
+          <t>664059</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>443278</t>
+          <t>439314</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>509512</t>
+          <t>504508</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1048573</t>
+          <t>1050803</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1149553</t>
+          <t>1151065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>447349</t>
+          <t>448132</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>517910</t>
+          <t>517913</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>328896</t>
+          <t>327751</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>391023</t>
+          <t>393442</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>794747</t>
+          <t>797219</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>887581</t>
+          <t>887942</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52191</t>
+          <t>52008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64789</t>
+          <t>65314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91875</t>
+          <t>92639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35938</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56744</t>
+          <t>57003</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52040</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77925</t>
+          <t>77231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>27093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47420</t>
+          <t>47601</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59460</t>
+          <t>58707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>32599</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>52098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74497</t>
+          <t>75688</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>104296</t>
+          <t>105473</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27408</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48158</t>
+          <t>48154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>27893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46967</t>
+          <t>47250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61081</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89060</t>
+          <t>88913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36564</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44796</t>
+          <t>42889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>87659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117580</t>
+          <t>117303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111180</t>
+          <t>112556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144691</t>
+          <t>146635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73854</t>
+          <t>73436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>103510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91940</t>
+          <t>92121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124539</t>
+          <t>125264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54289</t>
+          <t>54665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85636</t>
+          <t>85175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>55187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94352</t>
+          <t>91625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133027</t>
+          <t>130518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181447</t>
+          <t>180428</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225026</t>
+          <t>221983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119386</t>
+          <t>121324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153827</t>
+          <t>154818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>311750</t>
+          <t>312294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>366282</t>
+          <t>364055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133289</t>
+          <t>132135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174036</t>
+          <t>172140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110302</t>
+          <t>109383</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145240</t>
+          <t>143756</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>253058</t>
+          <t>254193</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>306550</t>
+          <t>306495</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>20519</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40606</t>
+          <t>41652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38206</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67402</t>
+          <t>65219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>111102</t>
+          <t>110612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142829</t>
+          <t>143101</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>81993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>111010</t>
+          <t>110652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>201918</t>
+          <t>203376</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>246043</t>
+          <t>244088</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68234</t>
+          <t>68810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98904</t>
+          <t>99735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78196</t>
+          <t>78005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106266</t>
+          <t>106983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153833</t>
+          <t>155009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>195574</t>
+          <t>193987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55132</t>
+          <t>53425</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55657</t>
+          <t>55875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73340</t>
+          <t>74340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>101045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120043</t>
+          <t>119766</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150913</t>
+          <t>150602</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44736</t>
+          <t>44919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69514</t>
+          <t>69332</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50004</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77818</t>
+          <t>80177</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>150516</t>
+          <t>152825</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>202921</t>
+          <t>203581</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>101245</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>141787</t>
+          <t>144678</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>268459</t>
+          <t>267738</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>332686</t>
+          <t>331927</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>535366</t>
+          <t>535240</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>605558</t>
+          <t>604248</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,82 +10448,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>46,22%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>52,18%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>425171</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>391254</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>454237</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>47,22%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>43,45%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>50,44%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>993992</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>951708</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1043623</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>48,29%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>46,23%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>52,29%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>425171</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>396063</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>454198</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>43,98%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>50,44%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>948</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>993992</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>946333</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1038188</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>48,29%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>45,97%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>380485</t>
+          <t>382771</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>445748</t>
+          <t>449307</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>322678</t>
+          <t>321357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>380689</t>
+          <t>381857</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>721579</t>
+          <t>715797</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>806485</t>
+          <t>806575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
